--- a/実装リスト完成版.xlsx
+++ b/実装リスト完成版.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Test\HotondoMenmoti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooharastudent-my.sharepoint.com/personal/mcd2576055_stu_o-hara_ac_jp/Documents/デスクトップ/Team GameMake/HotondoMenmoti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="833" documentId="13_ncr:1_{771383A5-F94D-48FD-A959-4286C3D86380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314C17D3-76D9-4016-9F3D-2E7161A0862A}"/>
+  <xr:revisionPtr revIDLastSave="852" documentId="13_ncr:1_{771383A5-F94D-48FD-A959-4286C3D86380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F65DCA-EEF4-4399-80A4-101C4E76A12A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="日程" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">記入例!$B$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">日程!$B$3:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">記入例!$B$2:$K$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,16 +32,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="310">
   <si>
     <t>実装要素洗い出し(例)</t>
     <rPh sb="0" eb="4">
@@ -2183,6 +2184,24 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンベース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンベース作成</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンベースを作成する</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2191,7 +2210,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2250,7 +2269,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
-      <charset val="1"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="12">
@@ -2321,7 +2341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2516,13 +2536,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2686,6 +2717,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2968,8 +3011,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:XFD1048576"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:XFD1048576"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
     <col min="2" max="2" width="3.75" customWidth="1"/>
@@ -2982,12 +3025,12 @@
     <col min="10" max="11" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3019,7 +3062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -3052,7 +3095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="15.75">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
@@ -3080,7 +3123,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="15.75">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
@@ -3108,7 +3151,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.75">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
@@ -3136,7 +3179,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
@@ -3167,7 +3210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15.75">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -3195,7 +3238,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15.75">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -3223,7 +3266,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15.75">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
@@ -3251,7 +3294,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15.75">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -3282,7 +3325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15.75">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
@@ -3310,7 +3353,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15.75">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -3338,7 +3381,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15.75">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
@@ -3366,7 +3409,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.75">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
@@ -3397,7 +3440,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15.75">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
@@ -3425,7 +3468,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
@@ -3453,7 +3496,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
@@ -3481,7 +3524,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
@@ -3509,7 +3552,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.75">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
@@ -3537,7 +3580,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="18.75" customHeight="1">
+    <row r="21" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="14"/>
       <c r="C21" s="1" t="s">
         <v>48</v>
@@ -3567,7 +3610,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="18.75" customHeight="1">
+    <row r="22" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="14"/>
       <c r="C22" s="1" t="s">
         <v>35</v>
@@ -3597,7 +3640,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="18.75" customHeight="1">
+    <row r="23" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="14"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
@@ -3625,7 +3668,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="18.75" customHeight="1">
+    <row r="24" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="14"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
@@ -3653,7 +3696,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="18.75" customHeight="1">
+    <row r="25" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="14"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
@@ -3681,7 +3724,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="18.75" customHeight="1">
+    <row r="26" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="14"/>
       <c r="C26" s="13"/>
       <c r="D26" s="1" t="s">
@@ -3709,7 +3752,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="18.75" customHeight="1">
+    <row r="27" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="14"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
@@ -3737,7 +3780,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="18.75" customHeight="1">
+    <row r="28" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="14"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
@@ -3765,7 +3808,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="18.75" customHeight="1">
+    <row r="29" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="14"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
@@ -3793,7 +3836,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="18.75" customHeight="1">
+    <row r="30" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="14"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
@@ -3821,7 +3864,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="18.75" customHeight="1">
+    <row r="31" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="14"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
@@ -3849,7 +3892,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="18.75" customHeight="1">
+    <row r="32" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="14"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
@@ -3877,7 +3920,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="33" spans="2:12" ht="18.75" customHeight="1">
+    <row r="33" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="14"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
@@ -3905,7 +3948,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="18.75" customHeight="1">
+    <row r="34" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="14"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35" t="s">
@@ -3936,7 +3979,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="2:12" ht="18.75" customHeight="1">
+    <row r="35" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="14"/>
       <c r="C35" s="35"/>
       <c r="D35" s="35" t="s">
@@ -3967,7 +4010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:12" ht="18.75" customHeight="1">
+    <row r="36" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="14"/>
       <c r="C36" s="35"/>
       <c r="D36" s="35" t="s">
@@ -3998,7 +4041,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="18.75" customHeight="1">
+    <row r="37" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="14"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
@@ -4026,7 +4069,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="18.75" customHeight="1">
+    <row r="38" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="14"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
@@ -4054,7 +4097,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="18.75" customHeight="1">
+    <row r="39" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="14"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
@@ -4082,7 +4125,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B40" s="14"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
@@ -4110,7 +4153,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="41" spans="2:12">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B41" s="14"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
@@ -4138,7 +4181,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="42" spans="2:12" ht="15.75">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B42" s="14"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
@@ -4166,7 +4209,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="43" spans="2:12">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
         <v>90</v>
@@ -4196,7 +4239,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="2:12">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
@@ -4224,7 +4267,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="2:12" ht="15.75">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B45" s="10"/>
       <c r="C45" s="29" t="s">
         <v>91</v>
@@ -4255,7 +4298,7 @@
       </c>
       <c r="L45" s="11"/>
     </row>
-    <row r="46" spans="2:12" ht="15.75">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B46" s="10"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
@@ -4284,7 +4327,7 @@
       </c>
       <c r="L46" s="11"/>
     </row>
-    <row r="47" spans="2:12" ht="15.75">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B47" s="10"/>
       <c r="C47" s="29"/>
       <c r="D47" s="29" t="s">
@@ -4313,7 +4356,7 @@
       </c>
       <c r="L47" s="11"/>
     </row>
-    <row r="48" spans="2:12" ht="15.75">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B48" s="10"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
@@ -4342,7 +4385,7 @@
       </c>
       <c r="L48" s="11"/>
     </row>
-    <row r="49" spans="2:12" ht="15.75">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B49" s="10"/>
       <c r="C49" s="29"/>
       <c r="D49" s="29" t="s">
@@ -4371,7 +4414,7 @@
       </c>
       <c r="L49" s="11"/>
     </row>
-    <row r="50" spans="2:12" ht="15.75">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B50" s="10"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
@@ -4400,7 +4443,7 @@
       </c>
       <c r="L50" s="11"/>
     </row>
-    <row r="51" spans="2:12" ht="15.75">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B51" s="10"/>
       <c r="C51" s="29"/>
       <c r="D51" s="29" t="s">
@@ -4429,7 +4472,7 @@
       </c>
       <c r="L51" s="11"/>
     </row>
-    <row r="52" spans="2:12" ht="15.75">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B52" s="10"/>
       <c r="D52" s="1" t="s">
         <v>92</v>
@@ -4457,7 +4500,7 @@
       </c>
       <c r="L52" s="11"/>
     </row>
-    <row r="53" spans="2:12" ht="15.75">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B53" s="10"/>
       <c r="C53" s="29"/>
       <c r="D53" s="29" t="s">
@@ -4486,7 +4529,7 @@
       </c>
       <c r="L53" s="11"/>
     </row>
-    <row r="54" spans="2:12" ht="15.75">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B54" s="10"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
@@ -4515,7 +4558,7 @@
       </c>
       <c r="L54" s="11"/>
     </row>
-    <row r="55" spans="2:12" ht="15.75">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B55" s="10"/>
       <c r="C55" s="29"/>
       <c r="D55" s="29" t="s">
@@ -4544,7 +4587,7 @@
       </c>
       <c r="L55" s="11"/>
     </row>
-    <row r="56" spans="2:12" ht="15.75">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B56" s="10"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
@@ -4573,7 +4616,7 @@
       </c>
       <c r="L56" s="11"/>
     </row>
-    <row r="57" spans="2:12" ht="15.75">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B57" s="10"/>
       <c r="C57" s="29"/>
       <c r="D57" s="29" t="s">
@@ -4602,7 +4645,7 @@
       </c>
       <c r="L57" s="11"/>
     </row>
-    <row r="58" spans="2:12" ht="15.75">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B58" s="10"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
@@ -4631,7 +4674,7 @@
       </c>
       <c r="L58" s="11"/>
     </row>
-    <row r="59" spans="2:12" ht="15.75">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B59" s="10"/>
       <c r="C59" s="29"/>
       <c r="D59" s="29" t="s">
@@ -4660,7 +4703,7 @@
       </c>
       <c r="L59" s="11"/>
     </row>
-    <row r="60" spans="2:12" ht="15.75">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B60" s="10"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
@@ -4689,7 +4732,7 @@
       </c>
       <c r="L60" s="11"/>
     </row>
-    <row r="61" spans="2:12" ht="15.75">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B61" s="10"/>
       <c r="C61" s="29"/>
       <c r="D61" s="29" t="s">
@@ -4718,7 +4761,7 @@
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" spans="2:12" ht="15.75">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B62" s="10"/>
       <c r="C62" s="32"/>
       <c r="D62" s="32" t="s">
@@ -4747,7 +4790,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="2:12" ht="15.75">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B63" s="10"/>
       <c r="C63" s="29"/>
       <c r="D63" s="29" t="s">
@@ -4776,7 +4819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4788,7 +4831,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="2:11" customFormat="1">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4800,7 +4843,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="2:11" customFormat="1">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B66" s="1"/>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -4812,134 +4855,134 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="2:11" customFormat="1">
-      <c r="B67" s="38"/>
-      <c r="C67" s="15" t="s">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B67" s="39"/>
+      <c r="C67" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="F67" s="15" t="s">
+      <c r="F67" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G67" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="H67" s="15" t="s">
+      <c r="H67" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="I67" s="15">
+      <c r="I67" s="37">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J67" s="7">
+      <c r="J67" s="54">
         <v>46125</v>
       </c>
-      <c r="K67" s="7">
+      <c r="K67" s="54">
         <v>46125</v>
       </c>
     </row>
-    <row r="68" spans="2:11" customFormat="1">
-      <c r="B68" s="38"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15" t="s">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B68" s="56"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H68" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="J68" s="7">
+        <v>46125</v>
+      </c>
+      <c r="K68" s="7">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B69" s="45"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E69" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="F69" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="G68" s="15" t="s">
+      <c r="G69" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="H68" s="15" t="s">
+      <c r="H69" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="I68" s="15">
+      <c r="I69" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J68" s="7">
+      <c r="J69" s="7">
         <v>46149</v>
       </c>
-      <c r="K68" s="7">
+      <c r="K69" s="7">
         <v>46149</v>
       </c>
     </row>
-    <row r="69" spans="2:11" customFormat="1">
-      <c r="B69" s="38"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15" t="s">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B70" s="38"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E70" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F69" s="15" t="s">
+      <c r="F70" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G69" s="15" t="s">
+      <c r="G70" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="H69" s="15" t="s">
+      <c r="H70" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I69" s="15">
+      <c r="I70" s="46">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J69" s="7">
+      <c r="J70" s="55">
         <v>46125</v>
       </c>
-      <c r="K69" s="7">
+      <c r="K70" s="55">
         <v>46125</v>
       </c>
     </row>
-    <row r="70" spans="2:11" customFormat="1">
-      <c r="B70" s="39"/>
-      <c r="C70" s="37"/>
-      <c r="D70" t="s">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B71" s="39"/>
+      <c r="C71" s="37"/>
+      <c r="D71" t="s">
         <v>130</v>
       </c>
-      <c r="E70" s="37" t="s">
+      <c r="E71" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="F70" s="37" t="s">
+      <c r="F71" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="G70" s="37" t="s">
+      <c r="G71" s="37" t="s">
         <v>134</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="I70" s="37">
-        <v>0.15</v>
-      </c>
-      <c r="J70" s="7">
-        <v>46126</v>
-      </c>
-      <c r="K70" s="7">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" customFormat="1">
-      <c r="B71" s="48"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G71" s="15" t="s">
-        <v>136</v>
       </c>
       <c r="H71" s="37" t="s">
         <v>77</v>
@@ -4954,50 +4997,50 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="72" spans="2:11" customFormat="1">
-      <c r="B72" s="49"/>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B72" s="48"/>
       <c r="C72" s="15"/>
       <c r="D72" s="15" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F72" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H72" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H72" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="I72" s="15">
-        <v>7.4999999999999997E-2</v>
+      <c r="I72" s="37">
+        <v>0.15</v>
       </c>
       <c r="J72" s="7">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="K72" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B73" s="45"/>
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B73" s="49"/>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="H73" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>77</v>
       </c>
       <c r="I73" s="15">
@@ -5010,76 +5053,76 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="74" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B74" s="38"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46" t="s">
+    <row r="74" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B74" s="45"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E74" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="F74" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="G74" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="H74" s="51" t="s">
-        <v>47</v>
+      <c r="E74" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H74" s="50" t="s">
+        <v>77</v>
       </c>
       <c r="I74" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J74" s="7">
-        <v>46149</v>
+        <v>46125</v>
       </c>
       <c r="K74" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B75" s="38"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15" t="s">
+      <c r="C75" s="46"/>
+      <c r="D75" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="E75" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F75" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G75" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="H75" s="50" t="s">
-        <v>77</v>
+      <c r="E75" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F75" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="G75" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="H75" s="51" t="s">
+        <v>47</v>
       </c>
       <c r="I75" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J75" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K75" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B76" s="38"/>
       <c r="C76" s="15"/>
       <c r="D76" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G76" s="47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H76" s="50" t="s">
         <v>77</v>
@@ -5088,32 +5131,32 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J76" s="7">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="K76" s="7">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B77" s="38"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F77" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G77" s="47" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H77" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="I77" s="37">
-        <v>0.15</v>
+      <c r="I77" s="15">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J77" s="7">
         <v>46128</v>
@@ -5122,20 +5165,20 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="78" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="78" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="38"/>
       <c r="C78" s="15"/>
       <c r="D78" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H78" s="50" t="s">
         <v>77</v>
@@ -5150,20 +5193,20 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="79" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="79" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B79" s="38"/>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F79" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H79" s="50" t="s">
         <v>77</v>
@@ -5172,26 +5215,26 @@
         <v>0.15</v>
       </c>
       <c r="J79" s="7">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="K79" s="7">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B80" s="38"/>
       <c r="C80" s="15"/>
       <c r="D80" s="15" t="s">
         <v>137</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F80" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H80" s="50" t="s">
         <v>77</v>
@@ -5206,109 +5249,109 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="81" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B81" s="39"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37" t="s">
+    <row r="81" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B81" s="38"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E81" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F81" s="37" t="s">
+      <c r="E81" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G81" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="H81" s="53" t="s">
+      <c r="G81" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="H81" s="50" t="s">
         <v>77</v>
       </c>
       <c r="I81" s="37">
         <v>0.15</v>
       </c>
-      <c r="J81" s="54">
+      <c r="J81" s="7">
         <v>46126</v>
       </c>
-      <c r="K81" s="54">
+      <c r="K81" s="7">
         <v>46126</v>
       </c>
     </row>
-    <row r="82" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B82" s="44"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15" t="s">
+    <row r="82" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B82" s="39"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G82" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="H82" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="I82" s="37">
+        <v>0.15</v>
+      </c>
+      <c r="J82" s="54">
+        <v>46126</v>
+      </c>
+      <c r="K82" s="54">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B83" s="44"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F83" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G83" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="H82" s="50" t="s">
+      <c r="H83" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="I82" s="15">
+      <c r="I83" s="15">
         <v>1.5</v>
       </c>
-      <c r="J82" s="7">
+      <c r="J83" s="7">
         <v>46133</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K83" s="7">
         <v>46133</v>
       </c>
     </row>
-    <row r="83" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B83" s="45"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="46" t="s">
+    <row r="84" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B84" s="45"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="E83" s="46" t="s">
+      <c r="E84" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="F83" s="46" t="s">
+      <c r="F84" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="G83" s="46" t="s">
+      <c r="G84" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="H83" s="46" t="s">
+      <c r="H84" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="I83" s="46">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="J83" s="7">
-        <v>46149</v>
-      </c>
-      <c r="K83" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B84" s="38"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="F84" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G84" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="H84" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I84" s="15">
+      <c r="I84" s="46">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J84" s="7">
@@ -5318,51 +5361,51 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="85" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="85" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B85" s="38"/>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I85" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J85" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K85" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B86" s="38"/>
       <c r="C86" s="15"/>
       <c r="D86" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="I86" s="15">
         <v>7.4999999999999997E-2</v>
@@ -5374,104 +5417,104 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="87" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="87" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B87" s="38"/>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I87" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J87" s="7">
-        <v>46149</v>
+        <v>46125</v>
       </c>
       <c r="K87" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B88" s="38"/>
       <c r="C88" s="15"/>
       <c r="D88" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H88" s="15" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I88" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J88" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K88" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B89" s="38"/>
       <c r="C89" s="15"/>
       <c r="D89" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H89" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I89" s="37">
-        <v>0.15</v>
+      <c r="I89" s="15">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J89" s="7">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="K89" s="7">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B90" s="38"/>
       <c r="C90" s="15"/>
       <c r="D90" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F90" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>16</v>
@@ -5486,20 +5529,20 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="91" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="91" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B91" s="38"/>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F91" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H91" s="15" t="s">
         <v>16</v>
@@ -5508,26 +5551,26 @@
         <v>0.15</v>
       </c>
       <c r="J91" s="7">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="K91" s="7">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B92" s="38"/>
       <c r="C92" s="15"/>
       <c r="D92" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F92" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H92" s="15" t="s">
         <v>16</v>
@@ -5535,83 +5578,83 @@
       <c r="I92" s="37">
         <v>0.15</v>
       </c>
-      <c r="J92" s="54">
+      <c r="J92" s="7">
         <v>46126</v>
       </c>
-      <c r="K92" s="54">
+      <c r="K92" s="7">
         <v>46126</v>
       </c>
     </row>
-    <row r="93" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B93" s="44"/>
+    <row r="93" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B93" s="38"/>
       <c r="C93" s="15"/>
       <c r="D93" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F93" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="H93" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="I93" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="J93" s="7">
-        <v>46133</v>
-      </c>
-      <c r="K93" s="7">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B94" s="38"/>
+        <v>180</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" s="37">
+        <v>0.15</v>
+      </c>
+      <c r="J93" s="54">
+        <v>46126</v>
+      </c>
+      <c r="K93" s="54">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B94" s="44"/>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F94" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>47</v>
+        <v>182</v>
+      </c>
+      <c r="H94" s="50" t="s">
+        <v>60</v>
       </c>
       <c r="I94" s="15">
-        <v>7.4999999999999997E-2</v>
+        <v>1.5</v>
       </c>
       <c r="J94" s="7">
-        <v>46149</v>
+        <v>46133</v>
       </c>
       <c r="K94" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B95" s="38"/>
       <c r="C95" s="15"/>
       <c r="D95" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F95" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H95" s="15" t="s">
         <v>47</v>
@@ -5626,51 +5669,51 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="96" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="96" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B96" s="38"/>
       <c r="C96" s="15"/>
       <c r="D96" s="15" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F96" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I96" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J96" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K96" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B97" s="38"/>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="I97" s="15">
         <v>7.4999999999999997E-2</v>
@@ -5682,104 +5725,104 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="98" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="98" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B98" s="38"/>
       <c r="C98" s="15"/>
       <c r="D98" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H98" s="15" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I98" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J98" s="7">
-        <v>46149</v>
+        <v>46125</v>
       </c>
       <c r="K98" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B99" s="38"/>
       <c r="C99" s="15"/>
       <c r="D99" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H99" s="15" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I99" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J99" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K99" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B100" s="38"/>
       <c r="C100" s="15"/>
       <c r="D100" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="H100" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I100" s="37">
-        <v>0.15</v>
+      <c r="I100" s="15">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J100" s="7">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="K100" s="7">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="38"/>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H101" s="15" t="s">
         <v>16</v>
@@ -5794,20 +5837,20 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="102" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="102" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B102" s="38"/>
       <c r="C102" s="15"/>
       <c r="D102" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="F102" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>16</v>
@@ -5816,26 +5859,26 @@
         <v>0.15</v>
       </c>
       <c r="J102" s="7">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="K102" s="7">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B103" s="38"/>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F103" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H103" s="15" t="s">
         <v>16</v>
@@ -5843,83 +5886,83 @@
       <c r="I103" s="37">
         <v>0.15</v>
       </c>
-      <c r="J103" s="54">
+      <c r="J103" s="7">
         <v>46126</v>
       </c>
-      <c r="K103" s="54">
+      <c r="K103" s="7">
         <v>46126</v>
       </c>
     </row>
-    <row r="104" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B104" s="44"/>
+    <row r="104" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B104" s="38"/>
       <c r="C104" s="15"/>
       <c r="D104" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F104" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="H104" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="I104" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="J104" s="7">
-        <v>46133</v>
-      </c>
-      <c r="K104" s="7">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B105" s="38"/>
+        <v>199</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="37">
+        <v>0.15</v>
+      </c>
+      <c r="J104" s="54">
+        <v>46126</v>
+      </c>
+      <c r="K104" s="54">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B105" s="44"/>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F105" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G105" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="H105" s="15" t="s">
-        <v>47</v>
+        <v>201</v>
+      </c>
+      <c r="H105" s="50" t="s">
+        <v>60</v>
       </c>
       <c r="I105" s="15">
-        <v>7.4999999999999997E-2</v>
+        <v>1.5</v>
       </c>
       <c r="J105" s="7">
-        <v>46149</v>
+        <v>46133</v>
       </c>
       <c r="K105" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B106" s="38"/>
       <c r="C106" s="15"/>
       <c r="D106" s="15" t="s">
         <v>187</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>47</v>
@@ -5934,216 +5977,216 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="107" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+    <row r="107" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B107" s="38"/>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F107" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G107" s="15" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I107" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J107" s="7">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="K107" s="7">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B108" s="38"/>
       <c r="C108" s="15"/>
       <c r="D108" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I108" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J108" s="7">
-        <v>46135</v>
+        <v>46125</v>
       </c>
       <c r="K108" s="7">
-        <v>46135</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B109" s="38"/>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I109" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J109" s="7">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="K109" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B110" s="38"/>
       <c r="C110" s="15"/>
       <c r="D110" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F110" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I110" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="J110" s="7">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="K110" s="7">
-        <v>46135</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B111" s="38"/>
       <c r="C111" s="15"/>
       <c r="D111" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H111" s="15" t="s">
         <v>60</v>
       </c>
       <c r="I111" s="15">
-        <v>6</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J111" s="7">
         <v>46135</v>
       </c>
       <c r="K111" s="7">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11" customFormat="1" ht="18.75" customHeight="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B112" s="38"/>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I112" s="37">
-        <v>0.15</v>
+        <v>60</v>
+      </c>
+      <c r="I112" s="15">
+        <v>6</v>
       </c>
       <c r="J112" s="7">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="K112" s="7">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="113" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B113" s="38"/>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F113" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H113" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I113" s="15">
-        <v>7.4999999999999997E-2</v>
+        <v>77</v>
+      </c>
+      <c r="I113" s="37">
+        <v>0.15</v>
       </c>
       <c r="J113" s="7">
-        <v>46149</v>
+        <v>46128</v>
       </c>
       <c r="K113" s="7">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="114" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B114" s="38"/>
       <c r="C114" s="15"/>
       <c r="D114" s="15" t="s">
         <v>206</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F114" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H114" s="15" t="s">
         <v>47</v>
@@ -6158,48 +6201,48 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="115" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B115" s="39"/>
-      <c r="C115" s="37"/>
-      <c r="D115" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="E115" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="F115" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="G115" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="H115" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="I115" s="37">
-        <v>1.5</v>
+    <row r="115" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B115" s="38"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I115" s="15">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J115" s="7">
-        <v>46132</v>
+        <v>46149</v>
       </c>
       <c r="K115" s="7">
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="116" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B116" s="39"/>
       <c r="C116" s="37"/>
       <c r="D116" s="37" t="s">
         <v>223</v>
       </c>
       <c r="E116" s="37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F116" s="37" t="s">
         <v>124</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H116" s="37" t="s">
         <v>60</v>
@@ -6214,54 +6257,54 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="117" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B117" s="44"/>
-      <c r="C117" s="15"/>
-      <c r="D117" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E117" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G117" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="H117" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I117" s="15">
+    <row r="117" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B117" s="39"/>
+      <c r="C117" s="37"/>
+      <c r="D117" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F117" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G117" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="H117" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I117" s="37">
         <v>1.5</v>
       </c>
       <c r="J117" s="7">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="K117" s="7">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="118" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B118" s="44"/>
       <c r="C118" s="15"/>
       <c r="D118" s="15" t="s">
         <v>228</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H118" s="15" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I118" s="15">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" s="7">
         <v>46129</v>
@@ -6270,26 +6313,26 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="119" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="119" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B119" s="44"/>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H119" s="15" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I119" s="15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J119" s="7">
         <v>46129</v>
@@ -6298,104 +6341,106 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="120" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="120" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B120" s="44"/>
       <c r="C120" s="15"/>
       <c r="D120" s="15" t="s">
         <v>233</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>128</v>
       </c>
       <c r="G120" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="J120" s="7">
+        <v>46129</v>
+      </c>
+      <c r="K120" s="7">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121"/>
+      <c r="B121" s="44"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G121" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H120" s="15"/>
-      <c r="I120" s="15">
+      <c r="H121" s="15"/>
+      <c r="I121" s="15">
         <v>1</v>
       </c>
-      <c r="J120" s="16"/>
-      <c r="K120" s="16"/>
-    </row>
-    <row r="121" spans="2:12" s="11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B121" s="23"/>
-      <c r="C121" s="23" t="s">
+      <c r="J121" s="16"/>
+      <c r="K121" s="16"/>
+      <c r="L121"/>
+    </row>
+    <row r="122" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="11"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D122" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="E121" s="23" t="s">
+      <c r="E122" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="F121" s="23" t="s">
+      <c r="F122" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="G121" s="23" t="s">
+      <c r="G122" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="H121" s="23" t="s">
+      <c r="H122" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I121" s="23">
+      <c r="I122" s="23">
         <v>0.01</v>
       </c>
-      <c r="J121" s="24">
+      <c r="J122" s="24">
         <v>46121</v>
       </c>
-      <c r="K121" s="24">
+      <c r="K122" s="24">
         <v>46121</v>
       </c>
-      <c r="L121" s="11" t="s">
+      <c r="L122" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B122" s="22"/>
-      <c r="C122" s="19"/>
-      <c r="D122" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="E122" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="F122" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="H122" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I122" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="J122" s="20">
-        <v>46125</v>
-      </c>
-      <c r="K122" s="20">
-        <v>46125</v>
-      </c>
-      <c r="L122" s="18"/>
-    </row>
-    <row r="123" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B123" s="22"/>
       <c r="C123" s="19"/>
       <c r="D123" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F123" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H123" s="19" t="s">
         <v>16</v>
@@ -6411,55 +6456,55 @@
       </c>
       <c r="L123" s="18"/>
     </row>
-    <row r="124" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="124" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B124" s="22"/>
       <c r="C124" s="19"/>
       <c r="D124" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I124" s="19">
         <v>0.3</v>
       </c>
       <c r="J124" s="20">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="K124" s="20">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="L124" s="18"/>
     </row>
-    <row r="125" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="125" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B125" s="22"/>
       <c r="C125" s="19"/>
       <c r="D125" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F125" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I125" s="19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J125" s="20">
         <v>46136</v>
@@ -6469,55 +6514,55 @@
       </c>
       <c r="L125" s="18"/>
     </row>
-    <row r="126" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="126" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B126" s="22"/>
       <c r="C126" s="19"/>
       <c r="D126" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F126" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I126" s="19">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J126" s="20">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="K126" s="20">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="L126" s="18"/>
     </row>
-    <row r="127" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="127" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B127" s="22"/>
       <c r="C127" s="19"/>
       <c r="D127" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F127" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H127" s="19" t="s">
         <v>16</v>
       </c>
       <c r="I127" s="19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J127" s="20">
         <v>46125</v>
@@ -6527,49 +6572,49 @@
       </c>
       <c r="L127" s="18"/>
     </row>
-    <row r="128" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="128" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B128" s="22"/>
       <c r="C128" s="19"/>
       <c r="D128" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F128" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I128" s="19">
         <v>0.1</v>
       </c>
       <c r="J128" s="20">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="K128" s="20">
-        <v>46136</v>
+        <v>46125</v>
       </c>
       <c r="L128" s="18"/>
     </row>
-    <row r="129" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="129" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B129" s="22"/>
       <c r="C129" s="19"/>
       <c r="D129" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F129" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H129" s="19" t="s">
         <v>60</v>
@@ -6585,20 +6630,20 @@
       </c>
       <c r="L129" s="18"/>
     </row>
-    <row r="130" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="130" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B130" s="22"/>
       <c r="C130" s="19"/>
       <c r="D130" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E130" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F130" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H130" s="19" t="s">
         <v>60</v>
@@ -6614,20 +6659,20 @@
       </c>
       <c r="L130" s="18"/>
     </row>
-    <row r="131" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="131" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B131" s="22"/>
       <c r="C131" s="19"/>
       <c r="D131" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F131" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H131" s="19" t="s">
         <v>60</v>
@@ -6643,26 +6688,26 @@
       </c>
       <c r="L131" s="18"/>
     </row>
-    <row r="132" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="132" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="22"/>
       <c r="C132" s="19"/>
       <c r="D132" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F132" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G132" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H132" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I132" s="19">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J132" s="20">
         <v>46136</v>
@@ -6673,55 +6718,55 @@
       <c r="L132" s="18"/>
       <c r="XFD132" s="7"/>
     </row>
-    <row r="133" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="133" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="22"/>
       <c r="C133" s="19"/>
       <c r="D133" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="F133" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I133" s="19">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J133" s="20">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="K133" s="20">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="L133" s="18"/>
     </row>
-    <row r="134" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="134" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B134" s="22"/>
       <c r="C134" s="19"/>
       <c r="D134" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E134" s="19" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F134" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H134" s="19" t="s">
         <v>45</v>
       </c>
       <c r="I134" s="19">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J134" s="20">
         <v>46149</v>
@@ -6731,49 +6776,49 @@
       </c>
       <c r="L134" s="18"/>
     </row>
-    <row r="135" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="135" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B135" s="22"/>
       <c r="C135" s="19"/>
       <c r="D135" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="F135" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I135" s="19">
         <v>0.3</v>
       </c>
       <c r="J135" s="20">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="K135" s="20">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="L135" s="18"/>
     </row>
-    <row r="136" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="136" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B136" s="22"/>
       <c r="C136" s="19"/>
       <c r="D136" s="19" t="s">
         <v>239</v>
       </c>
       <c r="E136" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F136" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H136" s="19" t="s">
         <v>16</v>
@@ -6789,20 +6834,20 @@
       </c>
       <c r="L136" s="18"/>
     </row>
-    <row r="137" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="137" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B137" s="22"/>
       <c r="C137" s="19"/>
       <c r="D137" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E137" s="21" t="s">
-        <v>265</v>
+      <c r="E137" s="19" t="s">
+        <v>263</v>
       </c>
       <c r="F137" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G137" s="21" t="s">
-        <v>266</v>
+      <c r="G137" s="19" t="s">
+        <v>264</v>
       </c>
       <c r="H137" s="19" t="s">
         <v>16</v>
@@ -6818,258 +6863,264 @@
       </c>
       <c r="L137" s="18"/>
     </row>
-    <row r="138" spans="2:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B138" s="10"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="10" t="s">
+    <row r="138" spans="1:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E138" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F138" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G138" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="H138" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="J138" s="20">
+        <v>46126</v>
+      </c>
+      <c r="K138" s="20">
+        <v>46126</v>
+      </c>
+      <c r="L138" s="18"/>
+    </row>
+    <row r="139" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="11"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="10"/>
+      <c r="D139" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="E139" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F138" s="10" t="s">
+      <c r="F139" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G138" s="10" t="s">
+      <c r="G139" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="H138" s="10" t="s">
+      <c r="H139" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I138" s="10">
+      <c r="I139" s="10">
         <v>0.01</v>
       </c>
-      <c r="J138" s="25">
+      <c r="J139" s="25">
         <v>46121</v>
       </c>
-      <c r="K138" s="25">
+      <c r="K139" s="25">
         <v>46121</v>
       </c>
-      <c r="L138" s="11" t="s">
+      <c r="L139" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B139" s="22"/>
-      <c r="C139" s="19"/>
-      <c r="D139" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="E139" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F139" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G139" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="H139" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I139" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="J139" s="20">
-        <v>46126</v>
-      </c>
-      <c r="K139" s="20">
-        <v>46126</v>
-      </c>
-      <c r="L139" s="18"/>
-    </row>
-    <row r="140" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="140" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B140" s="22"/>
       <c r="C140" s="19"/>
       <c r="D140" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E140" s="19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F140" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I140" s="19">
         <v>0.3</v>
       </c>
       <c r="J140" s="20">
+        <v>46126</v>
+      </c>
+      <c r="K140" s="20">
+        <v>46126</v>
+      </c>
+      <c r="L140" s="18"/>
+    </row>
+    <row r="141" spans="1:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141"/>
+      <c r="B141" s="22"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G141" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="H141" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I141" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="J141" s="20">
         <v>46132</v>
       </c>
-      <c r="K140" s="20">
+      <c r="K141" s="20">
         <v>46132</v>
       </c>
-      <c r="L140" s="18"/>
-    </row>
-    <row r="141" spans="2:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B141" s="10"/>
-      <c r="C141" s="10"/>
-      <c r="D141" s="10" t="s">
+      <c r="L141" s="18"/>
+    </row>
+    <row r="142" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="11"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E141" s="10" t="s">
+      <c r="E142" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="F141" s="10" t="s">
+      <c r="F142" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G141" s="10" t="s">
+      <c r="G142" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="H141" s="10" t="s">
+      <c r="H142" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I141" s="10">
+      <c r="I142" s="10">
         <v>0.01</v>
       </c>
-      <c r="J141" s="25">
+      <c r="J142" s="25">
         <v>46121</v>
       </c>
-      <c r="K141" s="25">
+      <c r="K142" s="25">
         <v>46121</v>
       </c>
-      <c r="L141" s="11" t="s">
+      <c r="L142" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B142" s="22"/>
-      <c r="C142" s="19"/>
-      <c r="D142" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="E142" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="F142" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G142" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="H142" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="I142" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="J142" s="20">
-        <v>46132</v>
-      </c>
-      <c r="K142" s="20">
-        <v>46132</v>
-      </c>
-      <c r="L142" s="18"/>
-    </row>
-    <row r="143" spans="2:12 16384:16384" customFormat="1" ht="18.75" customHeight="1">
+    <row r="143" spans="1:12 16384:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B143" s="22"/>
       <c r="C143" s="19"/>
       <c r="D143" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E143" s="19" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="F143" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H143" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I143" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="J143" s="20">
+        <v>46132</v>
+      </c>
+      <c r="K143" s="20">
+        <v>46132</v>
+      </c>
+      <c r="L143" s="18"/>
+    </row>
+    <row r="144" spans="1:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A144"/>
+      <c r="B144" s="22"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E144" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F144" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G144" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H144" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I144" s="19">
         <v>0.3</v>
       </c>
-      <c r="J143" s="20">
+      <c r="J144" s="20">
         <v>46133</v>
       </c>
-      <c r="K143" s="20">
+      <c r="K144" s="20">
         <v>46133</v>
       </c>
-      <c r="L143" s="18"/>
-    </row>
-    <row r="144" spans="2:12 16384:16384" s="11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B144" s="10"/>
-      <c r="C144" s="10"/>
-      <c r="D144" s="10" t="s">
+      <c r="L144" s="18"/>
+    </row>
+    <row r="145" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="11"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E144" s="10" t="s">
+      <c r="E145" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F144" s="10" t="s">
+      <c r="F145" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G144" s="10" t="s">
+      <c r="G145" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="H144" s="10" t="s">
+      <c r="H145" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I144" s="10">
+      <c r="I145" s="10">
         <v>0.01</v>
       </c>
-      <c r="J144" s="25">
+      <c r="J145" s="25">
         <v>46121</v>
       </c>
-      <c r="K144" s="25">
+      <c r="K145" s="25">
         <v>46121</v>
       </c>
-      <c r="L144" s="11" t="s">
+      <c r="L145" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B145" s="22"/>
-      <c r="C145" s="19"/>
-      <c r="D145" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G145" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="H145" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I145" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="J145" s="20">
-        <v>46128</v>
-      </c>
-      <c r="K145" s="20">
-        <v>46128</v>
-      </c>
-      <c r="L145" s="18"/>
-    </row>
-    <row r="146" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="146" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B146" s="22"/>
       <c r="C146" s="19"/>
       <c r="D146" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="F146" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H146" s="19" t="s">
         <v>16</v>
@@ -7085,221 +7136,248 @@
       </c>
       <c r="L146" s="18"/>
     </row>
-    <row r="147" spans="2:12" s="11" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B147" s="10"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="10" t="s">
+    <row r="147" spans="1:12" s="11" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A147"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="E147" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G147" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="H147" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="J147" s="20">
+        <v>46128</v>
+      </c>
+      <c r="K147" s="20">
+        <v>46128</v>
+      </c>
+      <c r="L147" s="18"/>
+    </row>
+    <row r="148" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="11"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="10"/>
+      <c r="D148" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E148" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F147" s="10" t="s">
+      <c r="F148" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G147" s="10" t="s">
+      <c r="G148" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="H147" s="10" t="s">
+      <c r="H148" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I147" s="10">
+      <c r="I148" s="10">
         <v>0.01</v>
       </c>
-      <c r="J147" s="25">
+      <c r="J148" s="25">
         <v>46121</v>
       </c>
-      <c r="K147" s="25">
+      <c r="K148" s="25">
         <v>46121</v>
       </c>
-      <c r="L147" s="11" t="s">
+      <c r="L148" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B148" s="22"/>
-      <c r="C148" s="19"/>
-      <c r="D148" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="E148" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F148" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G148" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="H148" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="I148" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="J148" s="20">
-        <v>46133</v>
-      </c>
-      <c r="K148" s="43">
-        <v>46133</v>
-      </c>
-      <c r="L148" s="18"/>
-    </row>
-    <row r="149" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+    <row r="149" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B149" s="22"/>
       <c r="C149" s="19"/>
       <c r="D149" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E149" s="19" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="F149" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H149" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I149" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="J149" s="41">
-        <v>46135</v>
-      </c>
-      <c r="K149" s="42">
-        <v>46135</v>
-      </c>
-      <c r="L149" s="40"/>
-    </row>
-    <row r="150" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+        <v>0.1</v>
+      </c>
+      <c r="J149" s="20">
+        <v>46133</v>
+      </c>
+      <c r="K149" s="43">
+        <v>46133</v>
+      </c>
+      <c r="L149" s="18"/>
+    </row>
+    <row r="150" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B150" s="22"/>
       <c r="C150" s="19"/>
       <c r="D150" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E150" s="19" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="F150" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H150" s="19" t="s">
         <v>60</v>
       </c>
       <c r="I150" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="J150" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="J150" s="41">
         <v>46135</v>
       </c>
-      <c r="K150" s="17">
+      <c r="K150" s="42">
         <v>46135</v>
       </c>
-      <c r="L150" s="18"/>
-    </row>
-    <row r="151" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
+      <c r="L150" s="40"/>
+    </row>
+    <row r="151" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B151" s="22"/>
       <c r="C151" s="19"/>
       <c r="D151" s="19" t="s">
         <v>267</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F151" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G151" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="H151" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I151" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="J151" s="20">
+        <v>46135</v>
+      </c>
+      <c r="K151" s="17">
+        <v>46135</v>
+      </c>
+      <c r="L151" s="18"/>
+    </row>
+    <row r="152" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B152" s="22"/>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E152" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="F152" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G152" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="H151" s="19" t="s">
+      <c r="H152" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I151" s="19">
+      <c r="I152" s="19">
         <v>0.3</v>
       </c>
-      <c r="J151" s="20">
+      <c r="J152" s="20">
         <v>46128</v>
       </c>
-      <c r="K151" s="20">
+      <c r="K152" s="20">
         <v>46128</v>
       </c>
-      <c r="L151" s="18"/>
-    </row>
-    <row r="152" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="4" t="s">
+      <c r="L152" s="18"/>
+    </row>
+    <row r="153" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="E153" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F152" s="4" t="s">
+      <c r="F153" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G152" s="4" t="s">
+      <c r="G153" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="H153" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="I152" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="J152" s="7">
-        <v>46122</v>
-      </c>
-      <c r="K152" s="7">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="153" spans="2:12" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B153" s="22"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="I153" s="1">
         <v>0.3</v>
       </c>
       <c r="J153" s="7">
+        <v>46122</v>
+      </c>
+      <c r="K153" s="7">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B154" s="22"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I154" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J154" s="7">
         <v>46133</v>
       </c>
-      <c r="K153" s="7">
+      <c r="K154" s="7">
         <v>46133</v>
       </c>
     </row>
-    <row r="154" spans="2:12" customFormat="1" ht="15.75"/>
-    <row r="155" spans="2:12" customFormat="1" ht="15.75"/>
-    <row r="156" spans="2:12" customFormat="1" ht="15.75"/>
-    <row r="159" spans="2:12" customFormat="1" ht="15.75"/>
-    <row r="166" customFormat="1" ht="15.75"/>
-    <row r="167" customFormat="1" ht="15.75"/>
-    <row r="169" customFormat="1" ht="15.75"/>
-    <row r="185" customFormat="1" ht="15.75"/>
-    <row r="201" customFormat="1"/>
-    <row r="1048559" customFormat="1" ht="15.75"/>
-    <row r="1048575" customFormat="1" ht="15.75"/>
-    <row r="1048576" customFormat="1" ht="15.75"/>
+    <row r="166" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="167" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="169" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="185" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="201" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="1048559" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="1048575" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="1048576" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <autoFilter ref="B2:K2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
@@ -7311,12 +7389,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98395B35-A73E-4CD4-A461-D4A3405A9DBD}">
   <dimension ref="B2:D47"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="25.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
@@ -7327,12 +7405,12 @@
         <v>298</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -7343,7 +7421,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -7354,7 +7432,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -7365,7 +7443,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -7376,7 +7454,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -7387,7 +7465,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -7398,7 +7476,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -7409,7 +7487,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -7420,7 +7498,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -7431,7 +7509,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="1">
         <v>10</v>
       </c>
@@ -7442,7 +7520,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="1">
         <v>11</v>
       </c>
@@ -7453,7 +7531,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="1">
         <v>12</v>
       </c>
@@ -7464,7 +7542,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="1">
         <v>13</v>
       </c>
@@ -7475,7 +7553,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B17" s="1">
         <v>14</v>
       </c>
@@ -7486,7 +7564,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B18" s="1">
         <v>15</v>
       </c>
@@ -7497,7 +7575,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B19" s="1">
         <v>16</v>
       </c>
@@ -7508,7 +7586,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="1">
         <v>17</v>
       </c>
@@ -7519,7 +7597,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B21" s="1">
         <v>18</v>
       </c>
@@ -7530,7 +7608,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B22" s="1">
         <v>19</v>
       </c>
@@ -7541,7 +7619,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B23" s="1">
         <v>20</v>
       </c>
@@ -7552,7 +7630,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B24" s="1">
         <v>21</v>
       </c>
@@ -7563,7 +7641,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="25" spans="2:4">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B25" s="1">
         <v>22</v>
       </c>
@@ -7574,7 +7652,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B26" s="1">
         <v>23</v>
       </c>
@@ -7585,7 +7663,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B27" s="1">
         <v>24</v>
       </c>
@@ -7596,7 +7674,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B28" s="1">
         <v>25</v>
       </c>
@@ -7607,7 +7685,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B29" s="1">
         <v>26</v>
       </c>
@@ -7618,7 +7696,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B30" s="1">
         <v>27</v>
       </c>
@@ -7629,7 +7707,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B31" s="1">
         <v>28</v>
       </c>
@@ -7640,7 +7718,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B32" s="1">
         <v>29</v>
       </c>
@@ -7651,7 +7729,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="1">
         <v>30</v>
       </c>
@@ -7662,7 +7740,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="1">
         <v>31</v>
       </c>
@@ -7673,7 +7751,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="1">
         <v>32</v>
       </c>
@@ -7684,7 +7762,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="1">
         <v>33</v>
       </c>
@@ -7695,7 +7773,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="1">
         <v>34</v>
       </c>
@@ -7706,7 +7784,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="1">
         <v>35</v>
       </c>
@@ -7717,7 +7795,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="1">
         <v>36</v>
       </c>
@@ -7728,7 +7806,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="1">
         <v>37</v>
       </c>
@@ -7739,7 +7817,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="1">
         <v>38</v>
       </c>
@@ -7750,7 +7828,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="1">
         <v>39</v>
       </c>
@@ -7761,7 +7839,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="1">
         <v>40</v>
       </c>
@@ -7772,7 +7850,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="1">
         <v>41</v>
       </c>
@@ -7783,21 +7861,21 @@
         <v>306</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="1">
         <v>42</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="2:4">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="1">
         <v>43</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="2:4">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -7814,12 +7892,9 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7961,23 +8036,53 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ABC9630-CB8F-42BD-83D3-3D790BF5C912}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ABC9630-CB8F-42BD-83D3-3D790BF5C912}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D831816C-01AD-4A6E-8C50-A2EEDA300F79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0E0AEA-542A-41B2-A444-6FCF6FE07D56}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2854766E-1C9E-4318-B016-EBA879B9B6A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2854766E-1C9E-4318-B016-EBA879B9B6A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d5bf2f36-8a25-452e-ad22-b00a438b129c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0E0AEA-542A-41B2-A444-6FCF6FE07D56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D831816C-01AD-4A6E-8C50-A2EEDA300F79}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>